--- a/AAII_Financials/Quarterly/CI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CI_QTR_FIN.xlsx
@@ -656,338 +656,344 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>71668000</v>
+      </c>
+      <c r="E8" s="3">
         <v>68494000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>72472000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>69748000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>67178000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>65502000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>65649000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>63694000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>60523000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>57255000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>51114000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>49048000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>48586000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>46461000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>45753000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>134765000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>45478000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>44006000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>45688000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>44356000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>43190000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>40972000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>41879000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>40870000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>39303000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>38294000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>38338000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>38607000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>38842000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>37956000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>14255000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>11458000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>11477000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>11380000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>10543000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>10495000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>10427000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>10481000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>9948000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>9881000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>65133000</v>
+      </c>
+      <c r="E9" s="3">
         <v>62024000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>66055000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>63372000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>61017000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>58896000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>59187000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>57092000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>54007000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>50871000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>44541000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>42566000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>42476000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>40505000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>40063000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>116955000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>39342000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>38085000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>39990000</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1048,68 +1054,71 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6535000</v>
+      </c>
+      <c r="E10" s="3">
         <v>6470000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6417000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6376000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6161000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6606000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6462000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6602000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6516000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6384000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6573000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6482000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6110000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5956000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5690000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>17810000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6136000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5921000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5698000</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1170,8 +1179,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1214,8 +1226,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1336,8 +1349,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1458,252 +1474,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>243000</v>
+      </c>
+      <c r="E14" s="3">
         <v>1125000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>379000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>148000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>110000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>375000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-100000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1085000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>111000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1892000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1789000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>249000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-20000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>202000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-1711000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>30000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>52000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>279000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>13000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>26000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>133000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-4015000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-106000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>144000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>251000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2000</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>13000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>12000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>6000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>2000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>7000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>4000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>389000</v>
+      </c>
+      <c r="E15" s="3">
         <v>390000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>463000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>436000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>422000</v>
       </c>
       <c r="H15" s="3">
         <v>422000</v>
       </c>
       <c r="I15" s="3">
+        <v>422000</v>
+      </c>
+      <c r="J15" s="3">
         <v>424000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>436000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>420000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>423000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>451000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>454000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>455000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>459000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>457000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1419000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>501000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>458000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>499000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>501000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>503000</v>
-      </c>
-      <c r="X15" s="3">
-        <v>495000</v>
       </c>
       <c r="Y15" s="3">
         <v>495000</v>
       </c>
       <c r="Z15" s="3">
+        <v>495000</v>
+      </c>
+      <c r="AA15" s="3">
         <v>493000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>496000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>498000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>735000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>734000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>737000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>743000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>136000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>48000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>24000</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>27000</v>
       </c>
       <c r="AK15" s="3">
         <v>27000</v>
       </c>
       <c r="AL15" s="3">
-        <v>28000</v>
+        <v>27000</v>
       </c>
       <c r="AM15" s="3">
         <v>28000</v>
       </c>
       <c r="AN15" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AO15" s="3">
         <v>32000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>36000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>37000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1743,252 +1768,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>68812000</v>
+      </c>
+      <c r="E17" s="3">
         <v>64742000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>69914000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>66958000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>64710000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>63117000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>63378000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>61041000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>58048000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>54962000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>48742000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>46605000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>46370000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>44514000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>44077000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>126329000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>43107000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>41818000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>44151000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>41994000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>40994000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>39145000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>36164000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>38730000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>36640000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>36506000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>36686000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>36433000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>36656000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>35716000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>13529000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>10425000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>10319000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>10105000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>9785000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>9671000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>9293000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>9591000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>9343000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>9139000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2856000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3752000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2558000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2790000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2468000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2385000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2271000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2653000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2475000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2293000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2372000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2443000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2216000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1947000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1676000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8436000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2371000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2188000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1537000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2362000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2196000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1827000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5715000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2140000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2663000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1788000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1652000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2174000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2186000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2240000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>726000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1033000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1158000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1275000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>758000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>824000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1134000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>890000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>605000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>742000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2031,68 +2063,69 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>-3000</v>
       </c>
       <c r="E20" s="3">
+        <v>357000</v>
+      </c>
+      <c r="F20" s="3">
         <v>62000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-16000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1000</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
         <v>-38000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-51000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>6000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-493000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-89000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-322000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>68000</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -2153,243 +2186,249 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4142000</v>
+        <v>3248000</v>
       </c>
       <c r="E21" s="3">
+        <v>3785000</v>
+      </c>
+      <c r="F21" s="3">
         <v>2959000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3242000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2891000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2807000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2733000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3093000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2898000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2716000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2874000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2896000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2671000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2406000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2417000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>10145000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3041000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2583000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2348000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3096000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2927000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2542000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6428000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2842000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3357000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2481000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2579000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3087000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3100000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3137000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>983000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1195000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1294000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1415000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>899000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>963000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1274000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1036000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>755000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>892000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>357000</v>
-      </c>
-      <c r="E22" s="3">
+        <v>359000</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3">
         <v>300000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>363000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>338000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>362000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>400000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>380000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>378000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>322000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>446000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>353000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>352000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>345000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>324000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>904000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>301000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>299000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>293000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>303000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>298000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>314000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>337000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>336000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>374000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>391000</v>
       </c>
       <c r="AC22" s="3">
         <v>391000</v>
       </c>
       <c r="AD22" s="3">
+        <v>391000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>411000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>428000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>452000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>498000</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI22" s="3">
+      <c r="AI22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>56000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>57000</v>
       </c>
-      <c r="AK22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AM22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN22" s="3">
-        <v>0</v>
+      <c r="AN22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AO22" s="3">
         <v>0</v>
@@ -2397,252 +2436,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2257000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2270000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1817000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2295000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2021000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1648000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2009000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1192000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1989000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>79000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>188000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1840000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1884000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1601000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1358000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7039000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1981000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1567000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1312000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2059000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1898000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1513000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5378000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1804000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2289000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1397000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1261000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1763000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1758000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1788000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>228000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1033000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1102000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1218000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>758000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>824000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1134000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>890000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>605000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>742000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>382000</v>
+      </c>
+      <c r="E24" s="3">
         <v>409000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>543000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>322000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>389000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>239000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>473000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>367000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>360000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>291000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-919000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>391000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>374000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>295000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>136000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1479000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>411000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>355000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>179000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>424000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>422000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>342000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1236000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>406000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>529000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>208000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>277000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>409000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>348000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>416000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>80000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>264000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>294000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>301000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>259000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>262000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>324000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>297000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>231000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>290000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2763,252 +2811,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1875000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1861000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1274000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1973000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1632000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1409000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1536000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>825000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1629000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-212000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1107000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1449000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1510000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1306000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1222000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5560000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1570000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1212000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1133000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1635000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1476000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1171000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4142000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1398000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1760000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1189000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>984000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1354000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1410000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1372000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>148000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>769000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>808000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>917000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>499000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>562000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>810000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>593000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>374000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>452000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1660000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1654000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1234000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1868000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1532000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1323000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1424000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>739000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1548000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-277000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1029000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1408000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1460000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1267000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1193000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5511000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1557000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1197000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1116000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1621000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1467000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1161000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4135000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1388000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1754000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1181000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>977000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1351000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1408000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1368000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>145000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>767000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>806000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>915000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>498000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>560000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>813000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>598000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>382000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>456000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3129,8 +3186,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3203,8 +3263,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -3221,24 +3281,24 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>5000</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-232000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3251,8 +3311,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3373,8 +3436,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3495,68 +3561,71 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>3000</v>
       </c>
       <c r="E32" s="3">
+        <v>-357000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-62000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>16000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1000</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
         <v>38000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>51000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>-6000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>493000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>89000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>322000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-68000</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -3617,130 +3686,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1660000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1654000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1234000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1868000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1532000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1323000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1424000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>739000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1548000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-277000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1029000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1408000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1460000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1267000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1193000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5511000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1557000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1197000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1116000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1621000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1467000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1161000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4135000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1388000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1754000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1181000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>977000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1351000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1408000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1368000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>144000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>772000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>806000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>915000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>266000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>560000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>813000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>598000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>382000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>456000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3861,257 +3936,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1660000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1654000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1234000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1868000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1532000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1323000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1424000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>739000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1548000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-277000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1029000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1408000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1460000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1267000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1193000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5511000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1557000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1197000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1116000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1621000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1467000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1161000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4135000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1388000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1754000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1181000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>977000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1351000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1408000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1368000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>144000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>772000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>806000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>915000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>266000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>560000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>813000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>598000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>382000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>456000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4154,8 +4238,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4198,190 +4283,194 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6298000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7040000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7676000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6025000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4329000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8334000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7550000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5888000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6788000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8439000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7822000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8497000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9585000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7935000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5924000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7079000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4421000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4424000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5081000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3483000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3821000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6505000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10182000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5344000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7185000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4452000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4619000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4577000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3610000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4976000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3855000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>24032000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3634000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2771000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2972000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3656000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>3611000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>4155000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>3185000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>3224000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>959000</v>
+      </c>
+      <c r="E42" s="3">
         <v>812000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1056000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>883000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>813000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>727000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>665000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>864000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1068000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1108000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>925000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1046000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>872000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>808000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>905000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>783000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>754000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>731000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>920000</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
       <c r="W42" s="3">
         <v>0</v>
       </c>
@@ -4442,68 +4531,71 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>30917000</v>
+      </c>
+      <c r="E43" s="3">
         <v>26729000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>28888000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>31848000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>31290000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>27075000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24227000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>27846000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>25293000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20729000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>17722000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>19321000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>18554000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>17704000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>17218000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>17275000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>18290000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>16003000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>15071000</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
@@ -4534,98 +4626,101 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH43" s="3">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI43" s="3">
         <v>3609000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3412000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3455000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3380000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3308000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3419000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3154000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3077000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>3577000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5847000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5831000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7338000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5632000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5967000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5176000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6692000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5083000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5173000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4630000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5645000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4416000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4514000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4211000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4777000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4017000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3781000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3500000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3722000</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
-      </c>
       <c r="W44" s="3">
         <v>0</v>
       </c>
@@ -4686,68 +4781,71 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2970000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2620000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2856000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2347000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2324000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2243000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9736000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9541000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7893000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8451000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5237000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1238000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1186000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1263000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1298000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1016000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10176000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10735000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>11340000</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
       <c r="W45" s="3">
         <v>0</v>
       </c>
@@ -4808,68 +4906,71 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>46991000</v>
+      </c>
+      <c r="E46" s="3">
         <v>43032000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>47814000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>46735000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>44723000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>43555000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>48870000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>49222000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>46215000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>43357000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>37351000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>34518000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>34711000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>31921000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>30122000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>30170000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>37422000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>35393000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>36134000</v>
       </c>
-      <c r="V46" s="3">
-        <v>0</v>
-      </c>
       <c r="W46" s="3">
         <v>0</v>
       </c>
@@ -4930,374 +5031,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>19037000</v>
+      </c>
+      <c r="E47" s="3">
         <v>18902000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>18471000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>18483000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>15662000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>15350000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>15128000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>15270000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>15944000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>16025000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>17985000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>18974000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>18967000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>16698000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>16288000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>16273000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>16724000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>17693000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>18438000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>41380000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>40389000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>37886000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>36784000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>36764000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>35222000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>33316000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>33195000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>41994000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>41545000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>39860000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>39447000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>28976000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>29339000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>29864000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>28619000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>28245000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>27932000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>27259000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>26815000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>27101000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3736000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3704000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>877000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3650000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3621000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3681000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>828000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3594000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3551000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3607000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>877000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3924000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3884000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3837000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7923000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4140000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4104000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4089000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4143000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4589000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4586000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4648000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4757000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4733000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4799000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4831000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4953000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5013000</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>5125000</v>
       </c>
       <c r="AF48" s="3">
         <v>5125000</v>
       </c>
       <c r="AG48" s="3">
+        <v>5125000</v>
+      </c>
+      <c r="AH48" s="3">
         <v>4562000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1559000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1554000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1552000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1563000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1526000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1509000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1519000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1536000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1561000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>72465000</v>
+      </c>
+      <c r="E49" s="3">
         <v>72852000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>76258000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>73899000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>73046000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>73417000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>76613000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>74165000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>74434000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>74749000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>77940000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>77134000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>77524000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>77913000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>78303000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>78692000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>79086000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>79518000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>79913000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>80671000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>81070000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>79427000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>79827000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>80177000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>80381000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>80746000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>81164000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>81546000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>82166000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>82875000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>84071000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>6129000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>6147000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>6170000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>6164000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>6001000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>6000000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>5982000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>5980000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>6007000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5418,8 +5531,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5540,130 +5656,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14853000</v>
+      </c>
+      <c r="E52" s="3">
         <v>14776000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14040000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15152000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14599000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14655000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13488000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15388000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15302000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15381000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>17553000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15095000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14968000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14789000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>18449000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>14934000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>15294000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>15917000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16261000</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
         <v>10022000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9788000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9419000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9512000</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG52" s="3">
-        <v>0</v>
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3">
         <v>132000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>140000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>96000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>39000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>172000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>199000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>263000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>304000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>110000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5784,130 +5906,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>157082000</v>
+      </c>
+      <c r="E54" s="3">
         <v>153266000</v>
-      </c>
-      <c r="E54" s="3">
-        <v>157919000</v>
       </c>
       <c r="F54" s="3">
         <v>157919000</v>
       </c>
       <c r="G54" s="3">
+        <v>157919000</v>
+      </c>
+      <c r="H54" s="3">
         <v>151651000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>150658000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>155881000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>157639000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>155446000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>153119000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>152761000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>149645000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>150054000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>147976000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>143885000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>144209000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>152630000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>152610000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>154889000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>154251000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>154207000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>152081000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>155451000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>160044000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>159628000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>154711000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>155774000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>154847000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>154401000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>154348000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>153226000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>82956000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>63102000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>63141000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>61759000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>61936000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>61738000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>61147000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>59360000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>60762000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5950,8 +6078,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5994,434 +6123,444 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36634000</v>
+      </c>
+      <c r="E57" s="3">
         <v>35642000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>40992000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>39647000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>39398000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>37736000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>37759000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>37316000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>36778000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>32402000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>28368000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>26993000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>26689000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>30716000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7775000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6870000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7142000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6632000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6655000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5659000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5647000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5640000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5478000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5327000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5413000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5585000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5090000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4502000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4517000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4488000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4366000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>7541000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>7406000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>7825000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>7290000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>6802000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>6601000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>6667000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>6414000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>6374000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2792000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1529000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>592000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3093000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4288000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3993000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3035000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2572000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1717000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1715000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2775000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3046000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4618000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3418000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2993000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3488000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2397000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2173000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2545000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2703000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1532000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>404000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3374000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>6449000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4750000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4340000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>5514000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4712000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2310000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2915000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2955000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>9000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>109000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>110000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>240000</v>
-      </c>
-      <c r="AL58" s="3">
-        <v>141000</v>
       </c>
       <c r="AM58" s="3">
         <v>141000</v>
       </c>
       <c r="AN58" s="3">
+        <v>141000</v>
+      </c>
+      <c r="AO58" s="3">
         <v>142000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>276000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>271000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9059000</v>
+      </c>
+      <c r="E59" s="3">
         <v>8857000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8050000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7782000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7828000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8045000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10698000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9352000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7875000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9003000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9733000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7352000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7539000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2919000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>38463000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>30757000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>35679000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>34857000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>34372000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>54164000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>53907000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>53418000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>53591000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>50205000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>49714000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>47335000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>47704000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>54151000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>54015000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>54212000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>52387000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>19869000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>20657000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>20622000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>17343000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>17872000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>17999000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>17816000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>17032000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>17805000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>55562000</v>
+      </c>
+      <c r="E60" s="3">
         <v>52606000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>56342000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>56453000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>56779000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>55745000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>57979000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>57060000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>55373000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>51977000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>48716000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>47059000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>47345000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>44727000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>41225000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>41115000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>45218000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>43662000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>43572000</v>
       </c>
-      <c r="V60" s="3">
-        <v>0</v>
-      </c>
       <c r="W60" s="3">
         <v>0</v>
       </c>
@@ -6482,226 +6621,232 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>29086000</v>
+      </c>
+      <c r="E61" s="3">
         <v>29371000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>30871000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>30947000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>26480000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>26455000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>28937000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>30230000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>30175000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>31053000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>28155000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>28094000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28115000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>29124000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>28100000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>28090000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>30984000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>31013000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>31125000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>31609000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>31606000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>31568000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>29545000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>29537000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>31774000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>32147000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>31893000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>34041000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>36885000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>37571000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>39523000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>25041000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5195000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5191000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5199000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5207000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>4622000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>4621000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>4756000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>4780000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>22750000</v>
+      </c>
+      <c r="E62" s="3">
         <v>21951000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>21647000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>21466000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>21136000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>21120000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>20716000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>21226000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>21390000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>21710000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22344000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>21223000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>21452000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>21822000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>32948000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>29871000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>30461000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>31771000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>33008000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8832000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8867000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8832000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8939000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>16337000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>16279000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>16109000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>16199000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9284000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>9407000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9403000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9453000</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI62" s="3" t="s">
         <v>5</v>
       </c>
@@ -6717,8 +6862,8 @@
       <c r="AM62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN62" s="3">
-        <v>0</v>
+      <c r="AN62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AO62" s="3">
         <v>0</v>
@@ -6726,8 +6871,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6848,8 +6996,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6970,8 +7121,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7092,130 +7246,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>114172000</v>
+      </c>
+      <c r="E66" s="3">
         <v>110824000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>116045000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>115905000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>111221000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>110244000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>114638000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>115341000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>113919000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>111769000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>106410000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>103879000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>104528000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>103380000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>99210000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>99168000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>106738000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>106523000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>107777000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>106836000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>105498000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>103932000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>105130000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>112012000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>112262000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>109632000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>110436000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>110151000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>110586000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>111940000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>112198000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>67401000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>48359000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>48946000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>48048000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>47791000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>47192000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>46921000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>45637000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>46788000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7258,8 +7418,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7380,8 +7541,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7502,8 +7666,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7624,8 +7791,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7746,130 +7916,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>50355000</v>
+      </c>
+      <c r="E72" s="3">
         <v>49106000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>47865000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>47028000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>45564000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>44434000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>43519000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>42480000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>42132000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>40978000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>41652000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>40982000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>39936000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>38841000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>37940000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>37041000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>34626000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>33420000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>32593000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>31803000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>30513000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>29389000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>28575000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>24440000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>23052000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>21298000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>20162000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19185000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>17834000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>16426000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>15088000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>18474000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>17722000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>16933000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>15800000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>15590000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>15102000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>14356000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>13855000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>13487000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7990,8 +8166,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8112,8 +8291,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8234,130 +8416,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>42620000</v>
+      </c>
+      <c r="E76" s="3">
         <v>42210000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>41713000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>41805000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>40214000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>40226000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>41033000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>42095000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>41332000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>41181000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>46223000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>45691000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>45445000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>44502000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>44675000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>45041000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>45892000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>46087000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>47112000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>47415000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>48709000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>48149000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>50321000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>48032000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>47366000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>45079000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>45338000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>44696000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>43815000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>42408000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>41028000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>15555000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14743000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>14195000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>13711000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>14145000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>14546000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>14226000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>13723000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>13974000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8478,257 +8666,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1660000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1654000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1234000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1868000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1532000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1323000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1424000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>739000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1548000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-277000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1029000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1408000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1460000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1267000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1193000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5511000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1557000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1197000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1116000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1621000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1467000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1161000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4135000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1388000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1754000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1181000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>977000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1351000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1408000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1368000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>144000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>772000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>806000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>915000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>266000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>560000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>813000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>598000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>382000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>456000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8771,130 +8968,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>260000</v>
+      </c>
+      <c r="E83" s="3">
         <v>252000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-375000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>214000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>318000</v>
       </c>
       <c r="H83" s="3">
         <v>318000</v>
       </c>
       <c r="I83" s="3">
+        <v>318000</v>
+      </c>
+      <c r="J83" s="3">
         <v>-458000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>312000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>290000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-345000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>266000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>258000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>259000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>735000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2202000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>759000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>717000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>743000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>734000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>731000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>715000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>713000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>702000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>694000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>693000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>927000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>913000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>914000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>897000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>257000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>162000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>136000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>140000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>141000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>139000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>140000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>146000</v>
-      </c>
-      <c r="AO83" s="3">
-        <v>150000</v>
       </c>
       <c r="AP83" s="3">
         <v>150000</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>150000</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9015,8 +9216,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9137,8 +9341,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9259,8 +9466,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9381,8 +9591,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9503,130 +9716,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-421000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1131000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6149000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3418000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1886000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1920000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5212000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>46000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>265000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4840000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1467000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2826000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2492000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5028000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2099000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6557000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1244000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2030000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4275000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2119000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-296000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1093000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>5092000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>515000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2856000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1887000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2793000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2461000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1039000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3192000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>126000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>624000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>995000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2025000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>575000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1235000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>697000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1579000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>952000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1807000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9669,130 +9888,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-297000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-267000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-322000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-278000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-285000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-327000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-337000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-399000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-370000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-365000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-403000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-397000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-408000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-345000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-338000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-324000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-288000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-304000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-350000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-258000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-242000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-319000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-252000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-256000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-310000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-243000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-303000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-194000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-182000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-126000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-117000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-103000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-131000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-146000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-103000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-91000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-99000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9913,8 +10136,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10035,130 +10261,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-503000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-637000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-420000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4387000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-797000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1197000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-191000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-776000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-640000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-495000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-440000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1337000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-414000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2983000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-616000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>3714000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-408000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-324000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>123000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-710000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2307000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-717000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>4420000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-938000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-237000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-269000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-271000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-304000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-634000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>475000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-24704000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>125000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-99000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1700000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-603000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-368000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-615000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-117000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-985000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1088000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10201,77 +10433,78 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>409000</v>
+      </c>
+      <c r="E96" s="3">
         <v>417000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>396000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>402000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>401000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>412000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>384000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>390000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>392000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>401000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>358000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>362000</v>
       </c>
       <c r="O96" s="3">
         <v>362000</v>
       </c>
       <c r="P96" s="3">
+        <v>362000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>368000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-334000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1050000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-352000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-357000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-324000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-330000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-342000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-345000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -10323,8 +10556,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10445,8 +10681,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10567,8 +10806,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10689,370 +10931,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>207000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1141000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4066000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2659000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1333000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3681000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3248000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>439000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2309000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2529000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1250000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2572000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-435000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2636000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8604000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-916000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2171000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2371000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1728000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-62000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4051000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4721000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1682000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-312000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1818000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1707000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1173000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1773000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2534000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>4400000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>19657000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-12000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-530000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-683000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-825000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-628000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-515000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>30000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E101" s="3">
         <v>9000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-26000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>18000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>14000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-7000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>12000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-18000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-57000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>12000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-98000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-57000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-23000</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-19000</v>
       </c>
       <c r="V101" s="3">
         <v>-19000</v>
       </c>
       <c r="W101" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="X101" s="3">
         <v>-1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>48000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>8000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>22000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-37000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>19000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-21000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>4000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>27000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>3000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>2000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>23000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-36000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-724000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-656000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1665000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1685000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3990000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-555000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1747000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-273000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2687000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1807000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-209000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1090000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1647000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2013000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1141000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1569000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-137000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-488000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2008000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-338000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2666000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3701000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4839000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2097000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2329000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-237000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>834000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>967000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1366000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1121000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-20177000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>20398000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>863000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-201000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-684000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>45000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-544000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>970000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-39000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>770000</v>
       </c>
     </row>
